--- a/artfynd/A 32686-2022 artfynd.xlsx
+++ b/artfynd/A 32686-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32686-2022 artfynd.xlsx
+++ b/artfynd/A 32686-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103022006</v>
+        <v>103021874</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -721,10 +716,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479639.2698443005</v>
+        <v>479668</v>
       </c>
       <c r="R2" t="n">
-        <v>6969933.425282116</v>
+        <v>6969959</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,19 +749,9 @@
           <t>2022-08-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,15 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103021874</v>
+        <v>103022006</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -828,7 +808,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>500</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -839,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479668.2325630113</v>
+        <v>479640</v>
       </c>
       <c r="R3" t="n">
-        <v>6969958.814111508</v>
+        <v>6969933</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,19 +852,9 @@
           <t>2022-08-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
